--- a/balance/LIFE-баланс.xlsx
+++ b/balance/LIFE-баланс.xlsx
@@ -30,12 +30,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3640" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3696" uniqueCount="838">
   <si>
     <t>ЖИЗНЬ — таблица баланса</t>
   </si>
   <si>
-    <t>Версия выгрузки: Альфа 0.15.2</t>
+    <t>Версия выгрузки: Альфа 0.16.0</t>
   </si>
   <si>
     <t>Дата: 2026-08-20</t>
@@ -1358,7 +1358,7 @@
     <t>шанс коалы</t>
   </si>
   <si>
-    <t>Шанс мутации зайца в коалу. Растёт с поколением.</t>
+    <t>Шанс мутации зайца в коалу. Равен шансу коровы, снижен: коала теперь стачивает лес.</t>
   </si>
   <si>
     <t>species.mutationChance.cow</t>
@@ -1367,7 +1367,7 @@
     <t>шанс коровы</t>
   </si>
   <si>
-    <t>Шанс мутации зайца в корову. Растёт с поколением.</t>
+    <t>Шанс мутации зайца в корову. Как у коалы.</t>
   </si>
   <si>
     <t>species.mutationChance.wolf</t>
@@ -1640,6 +1640,15 @@
     <t>Поведение</t>
   </si>
   <si>
+    <t>species.behavior.wolfCowPriority</t>
+  </si>
+  <si>
+    <t>приоритет коровы</t>
+  </si>
+  <si>
+    <t>Насколько волк предпочитает корову зайцу. 12 ≈ любая корова в поле зрения важнее ближайшего зайца.</t>
+  </si>
+  <si>
     <t>species.behavior.elkPoopInterval</t>
   </si>
   <si>
@@ -1661,6 +1670,15 @@
     <t>Радиус поиска чащи, когда коала прячется.</t>
   </si>
   <si>
+    <t>species.behavior.koalaTreeDowngradeGens</t>
+  </si>
+  <si>
+    <t>стачивание дерева</t>
+  </si>
+  <si>
+    <t>Сколько циклов коала сидит на дереве, прежде чем оно станет кустом. Потом идёт к следующему дереву.</t>
+  </si>
+  <si>
     <t>species.behavior.koalaPerchCapacity.tree</t>
   </si>
   <si>
@@ -1787,16 +1805,25 @@
     <t>сытость с куста</t>
   </si>
   <si>
-    <t>Энергия за один укус куста.</t>
-  </si>
-  <si>
-    <t>ecology.plants.treeBitesCow</t>
-  </si>
-  <si>
-    <t>укусы коровы</t>
-  </si>
-  <si>
-    <t>Запас укусов дерева для коровы (ещё × укусов за цикл).</t>
+    <t>Энергия за один укус куста (зайцы и прочие).</t>
+  </si>
+  <si>
+    <t>ecology.plants.bushBitesPerTickCow</t>
+  </si>
+  <si>
+    <t>укусы коровы/цикл</t>
+  </si>
+  <si>
+    <t>Сколько укусов куста корова делает за цикл. 2 укуса × 4 запаса = куст за 2 цикла (вдвое быстрее старого дерева).</t>
+  </si>
+  <si>
+    <t>ecology.plants.bushEnergyPerBiteCow</t>
+  </si>
+  <si>
+    <t>сытость коровы с куста</t>
+  </si>
+  <si>
+    <t>Энергия коровы за укус куста. 4×2.5 = 10 с куста.</t>
   </si>
   <si>
     <t>ecology.plants.treeBitesElk</t>
@@ -1817,24 +1844,6 @@
     <t>Базовая энергия за укус дерева (лось и прочие).</t>
   </si>
   <si>
-    <t>ecology.plants.treeEnergyPerBiteCow</t>
-  </si>
-  <si>
-    <t>сытость коровы</t>
-  </si>
-  <si>
-    <t>Энергия за укус дерева коровой.</t>
-  </si>
-  <si>
-    <t>ecology.plants.treeBitesPerTickCow</t>
-  </si>
-  <si>
-    <t>укусы коровы/цикл</t>
-  </si>
-  <si>
-    <t>Сколько укусов дерева корова делает за цикл (~4 цикла на дерево при 10×3).</t>
-  </si>
-  <si>
     <t>ecology.plants.bushToTreeGrass</t>
   </si>
   <si>
@@ -1850,7 +1859,7 @@
     <t>сытость коалы</t>
   </si>
   <si>
-    <t>Энергия коалы за укус листвы. Дерево от коалы не умирает.</t>
+    <t>Энергия коалы за укус листвы, пока она стачивает дерево в куст.</t>
   </si>
   <si>
     <t>ecology.decay.herb.radius</t>
@@ -1953,6 +1962,33 @@
   </si>
   <si>
     <t>Бонус роста от помёта лося (0.3 = +30%).</t>
+  </si>
+  <si>
+    <t>ecology.cowManure.ttl</t>
+  </si>
+  <si>
+    <t>навоз коровы TTL</t>
+  </si>
+  <si>
+    <t>Сколько циклов лежит удобрение на месте съеденного куста.</t>
+  </si>
+  <si>
+    <t>ecology.cowManure.strength</t>
+  </si>
+  <si>
+    <t>навоз коровы %</t>
+  </si>
+  <si>
+    <t>Бонус роста растений вокруг (0.5 = +50%).</t>
+  </si>
+  <si>
+    <t>ecology.cowManure.radius</t>
+  </si>
+  <si>
+    <t>навоз коровы R</t>
+  </si>
+  <si>
+    <t>Радиус «вокруг» в клетках (1 = клетка и 8 соседей).</t>
   </si>
   <si>
     <t>ecology.mushrooms.cowInterval</t>
@@ -3372,57 +3408,57 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>3</v>
@@ -3472,7 +3508,7 @@
     </row>
     <row r="3" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>57</v>
@@ -3522,7 +3558,7 @@
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>60</v>
@@ -3572,7 +3608,7 @@
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>63</v>
@@ -3622,7 +3658,7 @@
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>426</v>
@@ -3672,7 +3708,7 @@
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>430</v>
@@ -3722,7 +3758,7 @@
     </row>
     <row r="8" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>433</v>
@@ -3772,7 +3808,7 @@
     </row>
     <row r="9" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>824</v>
+        <v>836</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>436</v>
@@ -3822,7 +3858,7 @@
     </row>
     <row r="10" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>825</v>
+        <v>837</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>421</v>
@@ -4084,7 +4120,7 @@
         <v>441</v>
       </c>
       <c r="C8" s="8">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>42</v>
@@ -4919,7 +4955,7 @@
   <sheetPr>
     <tabColor rgb="FF548235"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -4992,16 +5028,16 @@
         <v>537</v>
       </c>
       <c r="C3" s="8">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>538</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>539</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>535</v>
@@ -5012,19 +5048,19 @@
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="8">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>541</v>
-      </c>
-      <c r="C4" s="8">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>533</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>542</v>
@@ -5050,7 +5086,7 @@
         <v>42</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>3</v>
+        <v>533</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>545</v>
@@ -5070,13 +5106,13 @@
         <v>547</v>
       </c>
       <c r="C6" s="8">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>3</v>
+        <v>246</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>548</v>
@@ -5096,7 +5132,7 @@
         <v>550</v>
       </c>
       <c r="C7" s="8">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>42</v>
@@ -5122,7 +5158,7 @@
         <v>553</v>
       </c>
       <c r="C8" s="8">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>42</v>
@@ -5140,8 +5176,60 @@
         <v>55</v>
       </c>
     </row>
+    <row r="9" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="C9" s="8">
+        <v>10</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="C10" s="8">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H8"/>
+  <autoFilter ref="A1:H10"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -5152,7 +5240,7 @@
   <sheetPr>
     <tabColor rgb="FF7F6000"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -5193,10 +5281,10 @@
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="C2" s="8">
         <v>10</v>
@@ -5208,10 +5296,10 @@
         <v>246</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>55</v>
@@ -5219,10 +5307,10 @@
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="C3" s="8">
         <v>28</v>
@@ -5234,10 +5322,10 @@
         <v>246</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>55</v>
@@ -5245,10 +5333,10 @@
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="C4" s="8">
         <v>113</v>
@@ -5260,10 +5348,10 @@
         <v>246</v>
       </c>
       <c r="F4" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>564</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>558</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>55</v>
@@ -5271,10 +5359,10 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C5" s="8">
         <v>0.037</v>
@@ -5286,10 +5374,10 @@
         <v>3</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>55</v>
@@ -5297,10 +5385,10 @@
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C6" s="8">
         <v>0.4</v>
@@ -5312,10 +5400,10 @@
         <v>3</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>55</v>
@@ -5323,10 +5411,10 @@
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C7" s="8">
         <v>0.33</v>
@@ -5338,10 +5426,10 @@
         <v>3</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>55</v>
@@ -5349,10 +5437,10 @@
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C8" s="8">
         <v>2</v>
@@ -5364,10 +5452,10 @@
         <v>3</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>55</v>
@@ -5375,10 +5463,10 @@
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="C9" s="8">
         <v>4</v>
@@ -5390,10 +5478,10 @@
         <v>3</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>55</v>
@@ -5401,10 +5489,10 @@
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="C10" s="8">
         <v>3.5</v>
@@ -5416,10 +5504,10 @@
         <v>3</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>55</v>
@@ -5427,10 +5515,10 @@
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="C11" s="8">
         <v>0.85</v>
@@ -5442,10 +5530,10 @@
         <v>3</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>55</v>
@@ -5453,13 +5541,13 @@
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="C12" s="8">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>42</v>
@@ -5468,10 +5556,10 @@
         <v>3</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>55</v>
@@ -5479,13 +5567,13 @@
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="C13" s="8">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>42</v>
@@ -5494,10 +5582,10 @@
         <v>3</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>55</v>
@@ -5505,13 +5593,13 @@
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="C14" s="8">
-        <v>0.45</v>
+        <v>8</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>42</v>
@@ -5520,10 +5608,10 @@
         <v>3</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>55</v>
@@ -5531,13 +5619,13 @@
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C15" s="8">
-        <v>2</v>
+        <v>0.45</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>42</v>
@@ -5546,10 +5634,10 @@
         <v>3</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>55</v>
@@ -5557,13 +5645,13 @@
     </row>
     <row r="16" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="C16" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>42</v>
@@ -5572,10 +5660,10 @@
         <v>3</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>55</v>
@@ -5583,13 +5671,13 @@
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="C17" s="8">
-        <v>2</v>
+        <v>0.85</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>42</v>
@@ -5598,43 +5686,17 @@
         <v>3</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>605</v>
-      </c>
-      <c r="C18" s="8">
-        <v>0.85</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H18"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -5645,7 +5707,7 @@
   <sheetPr>
     <tabColor rgb="FF7F6000"/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -5686,10 +5748,10 @@
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C2" s="8">
         <v>2</v>
@@ -5701,10 +5763,10 @@
         <v>533</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>55</v>
@@ -5712,10 +5774,10 @@
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C3" s="8">
         <v>0.08</v>
@@ -5727,10 +5789,10 @@
         <v>3</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>613</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>610</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>55</v>
@@ -5738,10 +5800,10 @@
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C4" s="8">
         <v>35</v>
@@ -5753,10 +5815,10 @@
         <v>246</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>55</v>
@@ -5764,10 +5826,10 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C5" s="8">
         <v>4</v>
@@ -5779,10 +5841,10 @@
         <v>533</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>55</v>
@@ -5790,10 +5852,10 @@
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C6" s="8">
         <v>0.14</v>
@@ -5805,10 +5867,10 @@
         <v>3</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>55</v>
@@ -5816,10 +5878,10 @@
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C7" s="8">
         <v>55</v>
@@ -5831,10 +5893,10 @@
         <v>246</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>55</v>
@@ -5842,10 +5904,10 @@
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C8" s="8">
         <v>5</v>
@@ -5857,10 +5919,10 @@
         <v>533</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>55</v>
@@ -5868,10 +5930,10 @@
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C9" s="8">
         <v>0.16</v>
@@ -5883,10 +5945,10 @@
         <v>3</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>55</v>
@@ -5894,10 +5956,10 @@
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C10" s="8">
         <v>62</v>
@@ -5909,10 +5971,10 @@
         <v>246</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>55</v>
@@ -5920,10 +5982,10 @@
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C11" s="8">
         <v>5</v>
@@ -5935,10 +5997,10 @@
         <v>246</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>55</v>
@@ -5946,10 +6008,10 @@
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C12" s="8">
         <v>0.3</v>
@@ -5961,10 +6023,10 @@
         <v>3</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>55</v>
@@ -5972,13 +6034,13 @@
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="C13" s="8">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>42</v>
@@ -5987,10 +6049,10 @@
         <v>246</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>55</v>
@@ -5998,13 +6060,13 @@
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C14" s="8">
-        <v>0.12</v>
+        <v>0.5</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>42</v>
@@ -6013,10 +6075,10 @@
         <v>3</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>55</v>
@@ -6024,25 +6086,25 @@
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C15" s="8">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>3</v>
+        <v>533</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>55</v>
@@ -6050,25 +6112,25 @@
     </row>
     <row r="16" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C16" s="8">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>3</v>
+        <v>246</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>55</v>
@@ -6076,13 +6138,13 @@
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C17" s="8">
-        <v>2</v>
+        <v>0.12</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>42</v>
@@ -6091,10 +6153,10 @@
         <v>3</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>55</v>
@@ -6102,13 +6164,13 @@
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C18" s="8">
-        <v>0.1</v>
+        <v>2.5</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>42</v>
@@ -6117,10 +6179,10 @@
         <v>3</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>55</v>
@@ -6128,32 +6190,110 @@
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C19" s="8">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="C20" s="8">
+        <v>2</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="C22" s="8">
         <v>0.05</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>610</v>
-      </c>
-      <c r="H19" s="5" t="s">
+      <c r="D22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H19"/>
+  <autoFilter ref="A1:H22"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -6205,10 +6345,10 @@
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="C2" s="8">
         <v>40</v>
@@ -6220,10 +6360,10 @@
         <v>246</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>55</v>
@@ -6231,10 +6371,10 @@
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="C3" s="8">
         <v>120</v>
@@ -6246,10 +6386,10 @@
         <v>246</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>55</v>
@@ -6257,10 +6397,10 @@
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>670</v>
+        <v>682</v>
       </c>
       <c r="C4" s="8">
         <v>60</v>
@@ -6272,10 +6412,10 @@
         <v>246</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>55</v>
@@ -6283,10 +6423,10 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="C5" s="8">
         <v>35</v>
@@ -6298,10 +6438,10 @@
         <v>246</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>55</v>
@@ -6309,10 +6449,10 @@
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="C6" s="8">
         <v>25</v>
@@ -6324,10 +6464,10 @@
         <v>246</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>677</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>665</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>55</v>
@@ -6335,10 +6475,10 @@
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="C7" s="8">
         <v>90</v>
@@ -6350,10 +6490,10 @@
         <v>246</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>55</v>
@@ -6361,10 +6501,10 @@
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="C8" s="8">
         <v>100</v>
@@ -6376,10 +6516,10 @@
         <v>246</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>55</v>
@@ -6387,10 +6527,10 @@
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="C9" s="8">
         <v>300</v>
@@ -6402,10 +6542,10 @@
         <v>246</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>55</v>
@@ -6464,10 +6604,10 @@
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="C2" s="8">
         <v>100</v>
@@ -6479,10 +6619,10 @@
         <v>246</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>55</v>
@@ -6490,10 +6630,10 @@
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="C3" s="8">
         <v>30</v>
@@ -6505,10 +6645,10 @@
         <v>3</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>55</v>
@@ -6516,10 +6656,10 @@
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="C4" s="8">
         <v>30</v>
@@ -6531,10 +6671,10 @@
         <v>3</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>55</v>
@@ -6542,10 +6682,10 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="C5" s="8">
         <v>25</v>
@@ -6557,10 +6697,10 @@
         <v>3</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>55</v>
@@ -6568,10 +6708,10 @@
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="C6" s="8">
         <v>15</v>
@@ -6583,10 +6723,10 @@
         <v>3</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>702</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>690</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>55</v>
@@ -6594,10 +6734,10 @@
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="C7" s="8">
         <v>0.1</v>
@@ -6609,10 +6749,10 @@
         <v>3</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>55</v>
@@ -6620,10 +6760,10 @@
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="C8" s="8">
         <v>0.3</v>
@@ -6635,10 +6775,10 @@
         <v>3</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>55</v>
@@ -6646,10 +6786,10 @@
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="C9" s="8">
         <v>0.1</v>
@@ -6661,10 +6801,10 @@
         <v>3</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>55</v>
@@ -6672,10 +6812,10 @@
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="C10" s="8">
         <v>0.5</v>
@@ -6687,10 +6827,10 @@
         <v>3</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>55</v>
@@ -6698,10 +6838,10 @@
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="C11" s="8">
         <v>0.1</v>
@@ -6713,10 +6853,10 @@
         <v>3</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>55</v>
@@ -6724,10 +6864,10 @@
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="C12" s="8">
         <v>0.3</v>
@@ -6739,10 +6879,10 @@
         <v>3</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>55</v>
@@ -6750,10 +6890,10 @@
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="C13" s="8">
         <v>0.5</v>
@@ -6765,10 +6905,10 @@
         <v>3</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>55</v>
@@ -6776,10 +6916,10 @@
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="C14" s="8">
         <v>1</v>
@@ -6791,10 +6931,10 @@
         <v>3</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>55</v>
@@ -6802,10 +6942,10 @@
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="C15" s="8">
         <v>0.0015</v>
@@ -6817,10 +6957,10 @@
         <v>3</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>55</v>
@@ -6828,10 +6968,10 @@
     </row>
     <row r="16" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="C16" s="8">
         <v>1.8</v>
@@ -6843,10 +6983,10 @@
         <v>3</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>55</v>
@@ -6854,10 +6994,10 @@
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="C17" s="8">
         <v>45</v>
@@ -6869,10 +7009,10 @@
         <v>3</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>55</v>
@@ -6880,10 +7020,10 @@
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="C18" s="8">
         <v>28</v>
@@ -6895,10 +7035,10 @@
         <v>3</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>55</v>
@@ -7015,7 +7155,7 @@
         <v>45</v>
       </c>
       <c r="C4" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>42</v>
@@ -7041,7 +7181,7 @@
         <v>48</v>
       </c>
       <c r="C5" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>42</v>
@@ -7071,7 +7211,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:H273"/>
+  <dimension ref="A1:H277"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -7170,7 +7310,7 @@
         <v>45</v>
       </c>
       <c r="C4" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>42</v>
@@ -7196,7 +7336,7 @@
         <v>48</v>
       </c>
       <c r="C5" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>42</v>
@@ -10888,7 +11028,7 @@
         <v>441</v>
       </c>
       <c r="C147" s="8">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>42</v>
@@ -11694,16 +11834,16 @@
         <v>537</v>
       </c>
       <c r="C178" s="8">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D178" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E178" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F178" s="5" t="s">
         <v>538</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>539</v>
       </c>
       <c r="G178" s="5" t="s">
         <v>535</v>
@@ -11714,19 +11854,19 @@
     </row>
     <row r="179" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="B179" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="B179" s="5" t="s">
+      <c r="C179" s="8">
+        <v>5</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E179" s="5" t="s">
         <v>541</v>
-      </c>
-      <c r="C179" s="8">
-        <v>1</v>
-      </c>
-      <c r="D179" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E179" s="5" t="s">
-        <v>533</v>
       </c>
       <c r="F179" s="5" t="s">
         <v>542</v>
@@ -11752,7 +11892,7 @@
         <v>42</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>3</v>
+        <v>533</v>
       </c>
       <c r="F180" s="5" t="s">
         <v>545</v>
@@ -11772,13 +11912,13 @@
         <v>547</v>
       </c>
       <c r="C181" s="8">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="D181" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>3</v>
+        <v>246</v>
       </c>
       <c r="F181" s="5" t="s">
         <v>548</v>
@@ -11798,7 +11938,7 @@
         <v>550</v>
       </c>
       <c r="C182" s="8">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D182" s="5" t="s">
         <v>42</v>
@@ -11824,7 +11964,7 @@
         <v>553</v>
       </c>
       <c r="C183" s="8">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D183" s="5" t="s">
         <v>42</v>
@@ -11856,13 +11996,13 @@
         <v>42</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>246</v>
+        <v>3</v>
       </c>
       <c r="F184" s="5" t="s">
         <v>557</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>558</v>
+        <v>535</v>
       </c>
       <c r="H184" s="5" t="s">
         <v>55</v>
@@ -11870,25 +12010,25 @@
     </row>
     <row r="185" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="B185" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="B185" s="5" t="s">
+      <c r="C185" s="8">
+        <v>2</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E185" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F185" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="C185" s="8">
-        <v>28</v>
-      </c>
-      <c r="D185" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E185" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="F185" s="5" t="s">
-        <v>561</v>
-      </c>
       <c r="G185" s="5" t="s">
-        <v>558</v>
+        <v>535</v>
       </c>
       <c r="H185" s="5" t="s">
         <v>55</v>
@@ -11896,13 +12036,13 @@
     </row>
     <row r="186" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="B186" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="B186" s="5" t="s">
-        <v>563</v>
-      </c>
       <c r="C186" s="8">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>42</v>
@@ -11911,10 +12051,10 @@
         <v>246</v>
       </c>
       <c r="F186" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="G186" s="5" t="s">
         <v>564</v>
-      </c>
-      <c r="G186" s="5" t="s">
-        <v>558</v>
       </c>
       <c r="H186" s="5" t="s">
         <v>55</v>
@@ -11928,19 +12068,19 @@
         <v>566</v>
       </c>
       <c r="C187" s="8">
-        <v>0.037</v>
+        <v>28</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>3</v>
+        <v>246</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>567</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H187" s="5" t="s">
         <v>55</v>
@@ -11954,19 +12094,19 @@
         <v>569</v>
       </c>
       <c r="C188" s="8">
-        <v>0.4</v>
+        <v>113</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>3</v>
+        <v>246</v>
       </c>
       <c r="F188" s="5" t="s">
         <v>570</v>
       </c>
       <c r="G188" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H188" s="5" t="s">
         <v>55</v>
@@ -11980,7 +12120,7 @@
         <v>572</v>
       </c>
       <c r="C189" s="8">
-        <v>0.33</v>
+        <v>0.037</v>
       </c>
       <c r="D189" s="5" t="s">
         <v>42</v>
@@ -11992,7 +12132,7 @@
         <v>573</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H189" s="5" t="s">
         <v>55</v>
@@ -12006,7 +12146,7 @@
         <v>575</v>
       </c>
       <c r="C190" s="8">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>42</v>
@@ -12018,7 +12158,7 @@
         <v>576</v>
       </c>
       <c r="G190" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H190" s="5" t="s">
         <v>55</v>
@@ -12032,7 +12172,7 @@
         <v>578</v>
       </c>
       <c r="C191" s="8">
-        <v>4</v>
+        <v>0.33</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>42</v>
@@ -12044,7 +12184,7 @@
         <v>579</v>
       </c>
       <c r="G191" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H191" s="5" t="s">
         <v>55</v>
@@ -12058,7 +12198,7 @@
         <v>581</v>
       </c>
       <c r="C192" s="8">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="D192" s="5" t="s">
         <v>42</v>
@@ -12070,7 +12210,7 @@
         <v>582</v>
       </c>
       <c r="G192" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H192" s="5" t="s">
         <v>55</v>
@@ -12084,7 +12224,7 @@
         <v>584</v>
       </c>
       <c r="C193" s="8">
-        <v>0.85</v>
+        <v>4</v>
       </c>
       <c r="D193" s="5" t="s">
         <v>42</v>
@@ -12096,7 +12236,7 @@
         <v>585</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H193" s="5" t="s">
         <v>55</v>
@@ -12110,7 +12250,7 @@
         <v>587</v>
       </c>
       <c r="C194" s="8">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="D194" s="5" t="s">
         <v>42</v>
@@ -12122,7 +12262,7 @@
         <v>588</v>
       </c>
       <c r="G194" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H194" s="5" t="s">
         <v>55</v>
@@ -12136,7 +12276,7 @@
         <v>590</v>
       </c>
       <c r="C195" s="8">
-        <v>8</v>
+        <v>0.85</v>
       </c>
       <c r="D195" s="5" t="s">
         <v>42</v>
@@ -12148,7 +12288,7 @@
         <v>591</v>
       </c>
       <c r="G195" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H195" s="5" t="s">
         <v>55</v>
@@ -12162,7 +12302,7 @@
         <v>593</v>
       </c>
       <c r="C196" s="8">
-        <v>0.45</v>
+        <v>2</v>
       </c>
       <c r="D196" s="5" t="s">
         <v>42</v>
@@ -12174,7 +12314,7 @@
         <v>594</v>
       </c>
       <c r="G196" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H196" s="5" t="s">
         <v>55</v>
@@ -12188,7 +12328,7 @@
         <v>596</v>
       </c>
       <c r="C197" s="8">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D197" s="5" t="s">
         <v>42</v>
@@ -12200,7 +12340,7 @@
         <v>597</v>
       </c>
       <c r="G197" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H197" s="5" t="s">
         <v>55</v>
@@ -12214,7 +12354,7 @@
         <v>599</v>
       </c>
       <c r="C198" s="8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D198" s="5" t="s">
         <v>42</v>
@@ -12226,7 +12366,7 @@
         <v>600</v>
       </c>
       <c r="G198" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H198" s="5" t="s">
         <v>55</v>
@@ -12240,7 +12380,7 @@
         <v>602</v>
       </c>
       <c r="C199" s="8">
-        <v>2</v>
+        <v>0.45</v>
       </c>
       <c r="D199" s="5" t="s">
         <v>42</v>
@@ -12252,7 +12392,7 @@
         <v>603</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H199" s="5" t="s">
         <v>55</v>
@@ -12266,7 +12406,7 @@
         <v>605</v>
       </c>
       <c r="C200" s="8">
-        <v>0.85</v>
+        <v>2</v>
       </c>
       <c r="D200" s="5" t="s">
         <v>42</v>
@@ -12278,7 +12418,7 @@
         <v>606</v>
       </c>
       <c r="G200" s="5" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="H200" s="5" t="s">
         <v>55</v>
@@ -12292,19 +12432,19 @@
         <v>608</v>
       </c>
       <c r="C201" s="8">
-        <v>2</v>
+        <v>0.85</v>
       </c>
       <c r="D201" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>533</v>
+        <v>3</v>
       </c>
       <c r="F201" s="5" t="s">
         <v>609</v>
       </c>
       <c r="G201" s="5" t="s">
-        <v>610</v>
+        <v>564</v>
       </c>
       <c r="H201" s="5" t="s">
         <v>55</v>
@@ -12312,25 +12452,25 @@
     </row>
     <row r="202" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="B202" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="B202" s="5" t="s">
+      <c r="C202" s="8">
+        <v>2</v>
+      </c>
+      <c r="D202" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E202" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="F202" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="C202" s="8">
-        <v>0.08</v>
-      </c>
-      <c r="D202" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E202" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F202" s="5" t="s">
+      <c r="G202" s="5" t="s">
         <v>613</v>
-      </c>
-      <c r="G202" s="5" t="s">
-        <v>610</v>
       </c>
       <c r="H202" s="5" t="s">
         <v>55</v>
@@ -12344,19 +12484,19 @@
         <v>615</v>
       </c>
       <c r="C203" s="8">
-        <v>35</v>
+        <v>0.08</v>
       </c>
       <c r="D203" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>246</v>
+        <v>3</v>
       </c>
       <c r="F203" s="5" t="s">
         <v>616</v>
       </c>
       <c r="G203" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H203" s="5" t="s">
         <v>55</v>
@@ -12370,19 +12510,19 @@
         <v>618</v>
       </c>
       <c r="C204" s="8">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="D204" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
       <c r="F204" s="5" t="s">
         <v>619</v>
       </c>
       <c r="G204" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H204" s="5" t="s">
         <v>55</v>
@@ -12396,19 +12536,19 @@
         <v>621</v>
       </c>
       <c r="C205" s="8">
-        <v>0.14</v>
+        <v>4</v>
       </c>
       <c r="D205" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>3</v>
+        <v>533</v>
       </c>
       <c r="F205" s="5" t="s">
         <v>622</v>
       </c>
       <c r="G205" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H205" s="5" t="s">
         <v>55</v>
@@ -12422,19 +12562,19 @@
         <v>624</v>
       </c>
       <c r="C206" s="8">
-        <v>55</v>
+        <v>0.14</v>
       </c>
       <c r="D206" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>246</v>
+        <v>3</v>
       </c>
       <c r="F206" s="5" t="s">
         <v>625</v>
       </c>
       <c r="G206" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H206" s="5" t="s">
         <v>55</v>
@@ -12448,19 +12588,19 @@
         <v>627</v>
       </c>
       <c r="C207" s="8">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="D207" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
       <c r="F207" s="5" t="s">
         <v>628</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H207" s="5" t="s">
         <v>55</v>
@@ -12474,19 +12614,19 @@
         <v>630</v>
       </c>
       <c r="C208" s="8">
-        <v>0.16</v>
+        <v>5</v>
       </c>
       <c r="D208" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>3</v>
+        <v>533</v>
       </c>
       <c r="F208" s="5" t="s">
         <v>631</v>
       </c>
       <c r="G208" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H208" s="5" t="s">
         <v>55</v>
@@ -12500,19 +12640,19 @@
         <v>633</v>
       </c>
       <c r="C209" s="8">
-        <v>62</v>
+        <v>0.16</v>
       </c>
       <c r="D209" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>246</v>
+        <v>3</v>
       </c>
       <c r="F209" s="5" t="s">
         <v>634</v>
       </c>
       <c r="G209" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H209" s="5" t="s">
         <v>55</v>
@@ -12526,7 +12666,7 @@
         <v>636</v>
       </c>
       <c r="C210" s="8">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="D210" s="5" t="s">
         <v>42</v>
@@ -12538,7 +12678,7 @@
         <v>637</v>
       </c>
       <c r="G210" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H210" s="5" t="s">
         <v>55</v>
@@ -12552,19 +12692,19 @@
         <v>639</v>
       </c>
       <c r="C211" s="8">
-        <v>0.3</v>
+        <v>5</v>
       </c>
       <c r="D211" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>3</v>
+        <v>246</v>
       </c>
       <c r="F211" s="5" t="s">
         <v>640</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H211" s="5" t="s">
         <v>55</v>
@@ -12578,19 +12718,19 @@
         <v>642</v>
       </c>
       <c r="C212" s="8">
-        <v>18</v>
+        <v>0.3</v>
       </c>
       <c r="D212" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>246</v>
+        <v>3</v>
       </c>
       <c r="F212" s="5" t="s">
         <v>643</v>
       </c>
       <c r="G212" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H212" s="5" t="s">
         <v>55</v>
@@ -12604,19 +12744,19 @@
         <v>645</v>
       </c>
       <c r="C213" s="8">
-        <v>0.12</v>
+        <v>8</v>
       </c>
       <c r="D213" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>3</v>
+        <v>246</v>
       </c>
       <c r="F213" s="5" t="s">
         <v>646</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H213" s="5" t="s">
         <v>55</v>
@@ -12630,7 +12770,7 @@
         <v>648</v>
       </c>
       <c r="C214" s="8">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="D214" s="5" t="s">
         <v>42</v>
@@ -12642,7 +12782,7 @@
         <v>649</v>
       </c>
       <c r="G214" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H214" s="5" t="s">
         <v>55</v>
@@ -12656,19 +12796,19 @@
         <v>651</v>
       </c>
       <c r="C215" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D215" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>3</v>
+        <v>533</v>
       </c>
       <c r="F215" s="5" t="s">
         <v>652</v>
       </c>
       <c r="G215" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H215" s="5" t="s">
         <v>55</v>
@@ -12682,19 +12822,19 @@
         <v>654</v>
       </c>
       <c r="C216" s="8">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D216" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>3</v>
+        <v>246</v>
       </c>
       <c r="F216" s="5" t="s">
         <v>655</v>
       </c>
       <c r="G216" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H216" s="5" t="s">
         <v>55</v>
@@ -12708,7 +12848,7 @@
         <v>657</v>
       </c>
       <c r="C217" s="8">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="D217" s="5" t="s">
         <v>42</v>
@@ -12720,7 +12860,7 @@
         <v>658</v>
       </c>
       <c r="G217" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H217" s="5" t="s">
         <v>55</v>
@@ -12734,7 +12874,7 @@
         <v>660</v>
       </c>
       <c r="C218" s="8">
-        <v>0.05</v>
+        <v>2.5</v>
       </c>
       <c r="D218" s="5" t="s">
         <v>42</v>
@@ -12746,7 +12886,7 @@
         <v>661</v>
       </c>
       <c r="G218" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H218" s="5" t="s">
         <v>55</v>
@@ -12760,19 +12900,19 @@
         <v>663</v>
       </c>
       <c r="C219" s="8">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D219" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>246</v>
+        <v>3</v>
       </c>
       <c r="F219" s="5" t="s">
         <v>664</v>
       </c>
       <c r="G219" s="5" t="s">
-        <v>665</v>
+        <v>613</v>
       </c>
       <c r="H219" s="5" t="s">
         <v>55</v>
@@ -12780,25 +12920,25 @@
     </row>
     <row r="220" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="B220" s="5" t="s">
         <v>666</v>
       </c>
-      <c r="B220" s="5" t="s">
+      <c r="C220" s="8">
+        <v>2</v>
+      </c>
+      <c r="D220" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E220" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F220" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="C220" s="8">
-        <v>120</v>
-      </c>
-      <c r="D220" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E220" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="F220" s="5" t="s">
-        <v>668</v>
-      </c>
       <c r="G220" s="5" t="s">
-        <v>665</v>
+        <v>613</v>
       </c>
       <c r="H220" s="5" t="s">
         <v>55</v>
@@ -12806,25 +12946,25 @@
     </row>
     <row r="221" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="B221" s="5" t="s">
         <v>669</v>
       </c>
-      <c r="B221" s="5" t="s">
+      <c r="C221" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="D221" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E221" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F221" s="5" t="s">
         <v>670</v>
       </c>
-      <c r="C221" s="8">
-        <v>60</v>
-      </c>
-      <c r="D221" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E221" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="F221" s="5" t="s">
-        <v>671</v>
-      </c>
       <c r="G221" s="5" t="s">
-        <v>665</v>
+        <v>613</v>
       </c>
       <c r="H221" s="5" t="s">
         <v>55</v>
@@ -12832,25 +12972,25 @@
     </row>
     <row r="222" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="B222" s="5" t="s">
         <v>672</v>
       </c>
-      <c r="B222" s="5" t="s">
+      <c r="C222" s="8">
+        <v>0.05</v>
+      </c>
+      <c r="D222" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E222" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F222" s="5" t="s">
         <v>673</v>
       </c>
-      <c r="C222" s="8">
-        <v>35</v>
-      </c>
-      <c r="D222" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E222" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="F222" s="5" t="s">
-        <v>674</v>
-      </c>
       <c r="G222" s="5" t="s">
-        <v>665</v>
+        <v>613</v>
       </c>
       <c r="H222" s="5" t="s">
         <v>55</v>
@@ -12858,13 +12998,13 @@
     </row>
     <row r="223" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="B223" s="5" t="s">
         <v>675</v>
       </c>
-      <c r="B223" s="5" t="s">
-        <v>676</v>
-      </c>
       <c r="C223" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D223" s="5" t="s">
         <v>42</v>
@@ -12873,10 +13013,10 @@
         <v>246</v>
       </c>
       <c r="F223" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="G223" s="5" t="s">
         <v>677</v>
-      </c>
-      <c r="G223" s="5" t="s">
-        <v>665</v>
       </c>
       <c r="H223" s="5" t="s">
         <v>55</v>
@@ -12890,7 +13030,7 @@
         <v>679</v>
       </c>
       <c r="C224" s="8">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D224" s="5" t="s">
         <v>42</v>
@@ -12902,7 +13042,7 @@
         <v>680</v>
       </c>
       <c r="G224" s="5" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="H224" s="5" t="s">
         <v>55</v>
@@ -12916,7 +13056,7 @@
         <v>682</v>
       </c>
       <c r="C225" s="8">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D225" s="5" t="s">
         <v>42</v>
@@ -12928,7 +13068,7 @@
         <v>683</v>
       </c>
       <c r="G225" s="5" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="H225" s="5" t="s">
         <v>55</v>
@@ -12942,7 +13082,7 @@
         <v>685</v>
       </c>
       <c r="C226" s="8">
-        <v>300</v>
+        <v>35</v>
       </c>
       <c r="D226" s="5" t="s">
         <v>42</v>
@@ -12954,7 +13094,7 @@
         <v>686</v>
       </c>
       <c r="G226" s="5" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="H226" s="5" t="s">
         <v>55</v>
@@ -12968,7 +13108,7 @@
         <v>688</v>
       </c>
       <c r="C227" s="8">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="D227" s="5" t="s">
         <v>42</v>
@@ -12980,7 +13120,7 @@
         <v>689</v>
       </c>
       <c r="G227" s="5" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="H227" s="5" t="s">
         <v>55</v>
@@ -12988,25 +13128,25 @@
     </row>
     <row r="228" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="B228" s="5" t="s">
         <v>691</v>
       </c>
-      <c r="B228" s="5" t="s">
+      <c r="C228" s="8">
+        <v>90</v>
+      </c>
+      <c r="D228" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E228" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F228" s="5" t="s">
         <v>692</v>
       </c>
-      <c r="C228" s="8">
-        <v>30</v>
-      </c>
-      <c r="D228" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E228" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F228" s="5" t="s">
-        <v>693</v>
-      </c>
       <c r="G228" s="5" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="H228" s="5" t="s">
         <v>55</v>
@@ -13014,25 +13154,25 @@
     </row>
     <row r="229" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="B229" s="5" t="s">
         <v>694</v>
       </c>
-      <c r="B229" s="5" t="s">
+      <c r="C229" s="8">
+        <v>100</v>
+      </c>
+      <c r="D229" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E229" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F229" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C229" s="8">
-        <v>30</v>
-      </c>
-      <c r="D229" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E229" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F229" s="5" t="s">
-        <v>696</v>
-      </c>
       <c r="G229" s="5" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="H229" s="5" t="s">
         <v>55</v>
@@ -13040,25 +13180,25 @@
     </row>
     <row r="230" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="B230" s="5" t="s">
         <v>697</v>
       </c>
-      <c r="B230" s="5" t="s">
+      <c r="C230" s="8">
+        <v>300</v>
+      </c>
+      <c r="D230" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E230" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F230" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="C230" s="8">
-        <v>25</v>
-      </c>
-      <c r="D230" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E230" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F230" s="5" t="s">
-        <v>699</v>
-      </c>
       <c r="G230" s="5" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="H230" s="5" t="s">
         <v>55</v>
@@ -13066,25 +13206,25 @@
     </row>
     <row r="231" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="B231" s="5" t="s">
         <v>700</v>
       </c>
-      <c r="B231" s="5" t="s">
+      <c r="C231" s="8">
+        <v>100</v>
+      </c>
+      <c r="D231" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E231" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F231" s="5" t="s">
         <v>701</v>
       </c>
-      <c r="C231" s="8">
-        <v>15</v>
-      </c>
-      <c r="D231" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E231" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F231" s="5" t="s">
+      <c r="G231" s="5" t="s">
         <v>702</v>
-      </c>
-      <c r="G231" s="5" t="s">
-        <v>690</v>
       </c>
       <c r="H231" s="5" t="s">
         <v>55</v>
@@ -13098,7 +13238,7 @@
         <v>704</v>
       </c>
       <c r="C232" s="8">
-        <v>0.1</v>
+        <v>30</v>
       </c>
       <c r="D232" s="5" t="s">
         <v>42</v>
@@ -13110,7 +13250,7 @@
         <v>705</v>
       </c>
       <c r="G232" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H232" s="5" t="s">
         <v>55</v>
@@ -13124,7 +13264,7 @@
         <v>707</v>
       </c>
       <c r="C233" s="8">
-        <v>0.3</v>
+        <v>30</v>
       </c>
       <c r="D233" s="5" t="s">
         <v>42</v>
@@ -13136,7 +13276,7 @@
         <v>708</v>
       </c>
       <c r="G233" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H233" s="5" t="s">
         <v>55</v>
@@ -13150,7 +13290,7 @@
         <v>710</v>
       </c>
       <c r="C234" s="8">
-        <v>0.1</v>
+        <v>25</v>
       </c>
       <c r="D234" s="5" t="s">
         <v>42</v>
@@ -13162,7 +13302,7 @@
         <v>711</v>
       </c>
       <c r="G234" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H234" s="5" t="s">
         <v>55</v>
@@ -13176,7 +13316,7 @@
         <v>713</v>
       </c>
       <c r="C235" s="8">
-        <v>0.5</v>
+        <v>15</v>
       </c>
       <c r="D235" s="5" t="s">
         <v>42</v>
@@ -13188,7 +13328,7 @@
         <v>714</v>
       </c>
       <c r="G235" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H235" s="5" t="s">
         <v>55</v>
@@ -13214,7 +13354,7 @@
         <v>717</v>
       </c>
       <c r="G236" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H236" s="5" t="s">
         <v>55</v>
@@ -13240,7 +13380,7 @@
         <v>720</v>
       </c>
       <c r="G237" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H237" s="5" t="s">
         <v>55</v>
@@ -13254,7 +13394,7 @@
         <v>722</v>
       </c>
       <c r="C238" s="8">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="D238" s="5" t="s">
         <v>42</v>
@@ -13266,7 +13406,7 @@
         <v>723</v>
       </c>
       <c r="G238" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H238" s="5" t="s">
         <v>55</v>
@@ -13280,7 +13420,7 @@
         <v>725</v>
       </c>
       <c r="C239" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D239" s="5" t="s">
         <v>42</v>
@@ -13292,7 +13432,7 @@
         <v>726</v>
       </c>
       <c r="G239" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H239" s="5" t="s">
         <v>55</v>
@@ -13306,7 +13446,7 @@
         <v>728</v>
       </c>
       <c r="C240" s="8">
-        <v>0.0015</v>
+        <v>0.1</v>
       </c>
       <c r="D240" s="5" t="s">
         <v>42</v>
@@ -13318,7 +13458,7 @@
         <v>729</v>
       </c>
       <c r="G240" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H240" s="5" t="s">
         <v>55</v>
@@ -13332,7 +13472,7 @@
         <v>731</v>
       </c>
       <c r="C241" s="8">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="D241" s="5" t="s">
         <v>42</v>
@@ -13344,7 +13484,7 @@
         <v>732</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H241" s="5" t="s">
         <v>55</v>
@@ -13358,7 +13498,7 @@
         <v>734</v>
       </c>
       <c r="C242" s="8">
-        <v>45</v>
+        <v>0.5</v>
       </c>
       <c r="D242" s="5" t="s">
         <v>42</v>
@@ -13370,7 +13510,7 @@
         <v>735</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H242" s="5" t="s">
         <v>55</v>
@@ -13384,7 +13524,7 @@
         <v>737</v>
       </c>
       <c r="C243" s="8">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D243" s="5" t="s">
         <v>42</v>
@@ -13396,7 +13536,7 @@
         <v>738</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="H243" s="5" t="s">
         <v>55</v>
@@ -13409,8 +13549,8 @@
       <c r="B244" s="5" t="s">
         <v>740</v>
       </c>
-      <c r="C244" s="7">
-        <v>2</v>
+      <c r="C244" s="8">
+        <v>0.0015</v>
       </c>
       <c r="D244" s="5" t="s">
         <v>42</v>
@@ -13422,62 +13562,62 @@
         <v>741</v>
       </c>
       <c r="G244" s="5" t="s">
-        <v>742</v>
+        <v>702</v>
       </c>
       <c r="H244" s="5" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="245" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="B245" s="5" t="s">
         <v>743</v>
       </c>
-      <c r="B245" s="5" t="s">
+      <c r="C245" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="D245" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E245" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F245" s="5" t="s">
         <v>744</v>
       </c>
-      <c r="C245" s="7">
-        <v>4</v>
-      </c>
-      <c r="D245" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E245" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F245" s="5" t="s">
-        <v>745</v>
-      </c>
       <c r="G245" s="5" t="s">
-        <v>742</v>
+        <v>702</v>
       </c>
       <c r="H245" s="5" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="246" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="B246" s="5" t="s">
         <v>746</v>
       </c>
-      <c r="B246" s="5" t="s">
+      <c r="C246" s="8">
+        <v>45</v>
+      </c>
+      <c r="D246" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E246" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F246" s="5" t="s">
         <v>747</v>
       </c>
-      <c r="C246" s="7">
-        <v>12</v>
-      </c>
-      <c r="D246" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E246" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F246" s="5" t="s">
-        <v>745</v>
-      </c>
       <c r="G246" s="5" t="s">
-        <v>742</v>
+        <v>702</v>
       </c>
       <c r="H246" s="5" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="247" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -13487,8 +13627,8 @@
       <c r="B247" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="C247" s="7">
-        <v>8</v>
+      <c r="C247" s="8">
+        <v>28</v>
       </c>
       <c r="D247" s="5" t="s">
         <v>42</v>
@@ -13497,24 +13637,24 @@
         <v>3</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="G247" s="5" t="s">
-        <v>742</v>
+        <v>702</v>
       </c>
       <c r="H247" s="5" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="248" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="5" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C248" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D248" s="5" t="s">
         <v>42</v>
@@ -13523,10 +13663,10 @@
         <v>3</v>
       </c>
       <c r="F248" s="5" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="G248" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H248" s="5" t="s">
         <v>39</v>
@@ -13534,13 +13674,13 @@
     </row>
     <row r="249" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="5" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="C249" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D249" s="5" t="s">
         <v>42</v>
@@ -13549,10 +13689,10 @@
         <v>3</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G249" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H249" s="5" t="s">
         <v>39</v>
@@ -13560,10 +13700,10 @@
     </row>
     <row r="250" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="5" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="C250" s="7">
         <v>12</v>
@@ -13575,10 +13715,10 @@
         <v>3</v>
       </c>
       <c r="F250" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G250" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H250" s="5" t="s">
         <v>39</v>
@@ -13586,25 +13726,25 @@
     </row>
     <row r="251" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="B251" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="C251" s="7">
+        <v>8</v>
+      </c>
+      <c r="D251" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E251" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F251" s="5" t="s">
         <v>757</v>
       </c>
-      <c r="C251" s="7">
-        <v>24</v>
-      </c>
-      <c r="D251" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E251" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F251" s="5" t="s">
-        <v>745</v>
-      </c>
       <c r="G251" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H251" s="5" t="s">
         <v>39</v>
@@ -13612,13 +13752,13 @@
     </row>
     <row r="252" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="5" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="C252" s="7">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D252" s="5" t="s">
         <v>42</v>
@@ -13627,10 +13767,10 @@
         <v>3</v>
       </c>
       <c r="F252" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G252" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H252" s="5" t="s">
         <v>39</v>
@@ -13638,13 +13778,13 @@
     </row>
     <row r="253" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="C253" s="7">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D253" s="5" t="s">
         <v>42</v>
@@ -13653,10 +13793,10 @@
         <v>3</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G253" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H253" s="5" t="s">
         <v>39</v>
@@ -13664,13 +13804,13 @@
     </row>
     <row r="254" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="5" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="C254" s="7">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D254" s="5" t="s">
         <v>42</v>
@@ -13679,10 +13819,10 @@
         <v>3</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G254" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H254" s="5" t="s">
         <v>39</v>
@@ -13690,13 +13830,13 @@
     </row>
     <row r="255" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="5" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="C255" s="7">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D255" s="5" t="s">
         <v>42</v>
@@ -13705,10 +13845,10 @@
         <v>3</v>
       </c>
       <c r="F255" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G255" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H255" s="5" t="s">
         <v>39</v>
@@ -13716,13 +13856,13 @@
     </row>
     <row r="256" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="C256" s="7">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D256" s="5" t="s">
         <v>42</v>
@@ -13731,10 +13871,10 @@
         <v>3</v>
       </c>
       <c r="F256" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G256" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H256" s="5" t="s">
         <v>39</v>
@@ -13742,13 +13882,13 @@
     </row>
     <row r="257" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="5" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="C257" s="7">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D257" s="5" t="s">
         <v>42</v>
@@ -13757,10 +13897,10 @@
         <v>3</v>
       </c>
       <c r="F257" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G257" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H257" s="5" t="s">
         <v>39</v>
@@ -13768,13 +13908,13 @@
     </row>
     <row r="258" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="5" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C258" s="7">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D258" s="5" t="s">
         <v>42</v>
@@ -13783,10 +13923,10 @@
         <v>3</v>
       </c>
       <c r="F258" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G258" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H258" s="5" t="s">
         <v>39</v>
@@ -13794,13 +13934,13 @@
     </row>
     <row r="259" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="5" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="C259" s="7">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D259" s="5" t="s">
         <v>42</v>
@@ -13809,10 +13949,10 @@
         <v>3</v>
       </c>
       <c r="F259" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G259" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H259" s="5" t="s">
         <v>39</v>
@@ -13820,13 +13960,13 @@
     </row>
     <row r="260" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="5" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C260" s="7">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D260" s="5" t="s">
         <v>42</v>
@@ -13835,10 +13975,10 @@
         <v>3</v>
       </c>
       <c r="F260" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G260" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H260" s="5" t="s">
         <v>39</v>
@@ -13846,13 +13986,13 @@
     </row>
     <row r="261" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="5" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="C261" s="7">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D261" s="5" t="s">
         <v>42</v>
@@ -13861,10 +14001,10 @@
         <v>3</v>
       </c>
       <c r="F261" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G261" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H261" s="5" t="s">
         <v>39</v>
@@ -13872,13 +14012,13 @@
     </row>
     <row r="262" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="5" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="C262" s="7">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D262" s="5" t="s">
         <v>42</v>
@@ -13887,10 +14027,10 @@
         <v>3</v>
       </c>
       <c r="F262" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G262" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H262" s="5" t="s">
         <v>39</v>
@@ -13898,13 +14038,13 @@
     </row>
     <row r="263" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="5" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="C263" s="7">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D263" s="5" t="s">
         <v>42</v>
@@ -13913,10 +14053,10 @@
         <v>3</v>
       </c>
       <c r="F263" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G263" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H263" s="5" t="s">
         <v>39</v>
@@ -13924,13 +14064,13 @@
     </row>
     <row r="264" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="5" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C264" s="7">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D264" s="5" t="s">
         <v>42</v>
@@ -13939,10 +14079,10 @@
         <v>3</v>
       </c>
       <c r="F264" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G264" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H264" s="5" t="s">
         <v>39</v>
@@ -13950,13 +14090,13 @@
     </row>
     <row r="265" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="C265" s="7">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D265" s="5" t="s">
         <v>42</v>
@@ -13965,10 +14105,10 @@
         <v>3</v>
       </c>
       <c r="F265" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G265" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H265" s="5" t="s">
         <v>39</v>
@@ -13976,13 +14116,13 @@
     </row>
     <row r="266" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="5" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="C266" s="7">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D266" s="5" t="s">
         <v>42</v>
@@ -13991,10 +14131,10 @@
         <v>3</v>
       </c>
       <c r="F266" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G266" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H266" s="5" t="s">
         <v>39</v>
@@ -14002,13 +14142,13 @@
     </row>
     <row r="267" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="5" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="C267" s="7">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D267" s="5" t="s">
         <v>42</v>
@@ -14017,10 +14157,10 @@
         <v>3</v>
       </c>
       <c r="F267" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G267" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H267" s="5" t="s">
         <v>39</v>
@@ -14028,13 +14168,13 @@
     </row>
     <row r="268" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="5" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="C268" s="7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D268" s="5" t="s">
         <v>42</v>
@@ -14043,10 +14183,10 @@
         <v>3</v>
       </c>
       <c r="F268" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G268" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H268" s="5" t="s">
         <v>39</v>
@@ -14054,13 +14194,13 @@
     </row>
     <row r="269" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C269" s="7">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D269" s="5" t="s">
         <v>42</v>
@@ -14069,10 +14209,10 @@
         <v>3</v>
       </c>
       <c r="F269" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G269" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H269" s="5" t="s">
         <v>39</v>
@@ -14080,13 +14220,13 @@
     </row>
     <row r="270" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="5" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="C270" s="7">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D270" s="5" t="s">
         <v>42</v>
@@ -14095,10 +14235,10 @@
         <v>3</v>
       </c>
       <c r="F270" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G270" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H270" s="5" t="s">
         <v>39</v>
@@ -14106,13 +14246,13 @@
     </row>
     <row r="271" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="5" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="C271" s="7">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D271" s="5" t="s">
         <v>42</v>
@@ -14121,10 +14261,10 @@
         <v>3</v>
       </c>
       <c r="F271" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G271" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H271" s="5" t="s">
         <v>39</v>
@@ -14132,13 +14272,13 @@
     </row>
     <row r="272" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="5" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C272" s="7">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D272" s="5" t="s">
         <v>42</v>
@@ -14147,10 +14287,10 @@
         <v>3</v>
       </c>
       <c r="F272" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G272" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H272" s="5" t="s">
         <v>39</v>
@@ -14158,13 +14298,13 @@
     </row>
     <row r="273" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="C273" s="7">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="D273" s="5" t="s">
         <v>42</v>
@@ -14173,17 +14313,121 @@
         <v>3</v>
       </c>
       <c r="F273" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G273" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H273" s="5" t="s">
         <v>39</v>
       </c>
     </row>
+    <row r="274" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A274" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="C274" s="7">
+        <v>8</v>
+      </c>
+      <c r="D274" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E274" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F274" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="G274" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="H274" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="275" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A275" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="C275" s="7">
+        <v>14</v>
+      </c>
+      <c r="D275" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E275" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F275" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="G275" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="H275" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="276" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A276" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="C276" s="7">
+        <v>30</v>
+      </c>
+      <c r="D276" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E276" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F276" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="G276" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="H276" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="277" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A277" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="C277" s="7">
+        <v>5</v>
+      </c>
+      <c r="D277" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E277" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F277" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="G277" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="H277" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H273"/>
+  <autoFilter ref="A1:H277"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -14235,10 +14479,10 @@
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="C2" s="7">
         <v>2</v>
@@ -14250,10 +14494,10 @@
         <v>3</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>39</v>
@@ -14261,10 +14505,10 @@
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
       <c r="C3" s="7">
         <v>4</v>
@@ -14276,10 +14520,10 @@
         <v>3</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>39</v>
@@ -14287,10 +14531,10 @@
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="C4" s="7">
         <v>12</v>
@@ -14302,10 +14546,10 @@
         <v>3</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>39</v>
@@ -14313,10 +14557,10 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="C5" s="7">
         <v>8</v>
@@ -14328,10 +14572,10 @@
         <v>3</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>39</v>
@@ -14339,10 +14583,10 @@
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="C6" s="7">
         <v>3</v>
@@ -14354,10 +14598,10 @@
         <v>3</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>39</v>
@@ -14365,10 +14609,10 @@
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="C7" s="7">
         <v>8</v>
@@ -14380,10 +14624,10 @@
         <v>3</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>39</v>
@@ -14391,10 +14635,10 @@
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="C8" s="7">
         <v>12</v>
@@ -14406,10 +14650,10 @@
         <v>3</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>39</v>
@@ -14417,10 +14661,10 @@
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
       <c r="C9" s="7">
         <v>24</v>
@@ -14432,10 +14676,10 @@
         <v>3</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>39</v>
@@ -14443,10 +14687,10 @@
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="C10" s="7">
         <v>14</v>
@@ -14458,10 +14702,10 @@
         <v>3</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>39</v>
@@ -14469,10 +14713,10 @@
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="C11" s="7">
         <v>20</v>
@@ -14484,10 +14728,10 @@
         <v>3</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>39</v>
@@ -14495,10 +14739,10 @@
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="C12" s="7">
         <v>22</v>
@@ -14510,10 +14754,10 @@
         <v>3</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>39</v>
@@ -14521,10 +14765,10 @@
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="C13" s="7">
         <v>30</v>
@@ -14536,10 +14780,10 @@
         <v>3</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>39</v>
@@ -14547,10 +14791,10 @@
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="C14" s="7">
         <v>40</v>
@@ -14562,10 +14806,10 @@
         <v>3</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>39</v>
@@ -14573,10 +14817,10 @@
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="C15" s="7">
         <v>5</v>
@@ -14588,10 +14832,10 @@
         <v>3</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>39</v>
@@ -14599,10 +14843,10 @@
     </row>
     <row r="16" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="C16" s="7">
         <v>8</v>
@@ -14614,10 +14858,10 @@
         <v>3</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>39</v>
@@ -14625,10 +14869,10 @@
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="C17" s="7">
         <v>18</v>
@@ -14640,10 +14884,10 @@
         <v>3</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>39</v>
@@ -14651,10 +14895,10 @@
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="C18" s="7">
         <v>10</v>
@@ -14666,10 +14910,10 @@
         <v>3</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>39</v>
@@ -14677,10 +14921,10 @@
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
       <c r="C19" s="7">
         <v>16</v>
@@ -14692,10 +14936,10 @@
         <v>3</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>39</v>
@@ -14703,10 +14947,10 @@
     </row>
     <row r="20" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
       <c r="C20" s="7">
         <v>20</v>
@@ -14718,10 +14962,10 @@
         <v>3</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>39</v>
@@ -14729,10 +14973,10 @@
     </row>
     <row r="21" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="C21" s="7">
         <v>35</v>
@@ -14744,10 +14988,10 @@
         <v>3</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>39</v>
@@ -14755,10 +14999,10 @@
     </row>
     <row r="22" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="C22" s="7">
         <v>35</v>
@@ -14770,10 +15014,10 @@
         <v>3</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>39</v>
@@ -14781,10 +15025,10 @@
     </row>
     <row r="23" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
       <c r="C23" s="7">
         <v>25</v>
@@ -14796,10 +15040,10 @@
         <v>3</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>39</v>
@@ -14807,10 +15051,10 @@
     </row>
     <row r="24" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="C24" s="7">
         <v>32</v>
@@ -14822,10 +15066,10 @@
         <v>3</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>39</v>
@@ -14833,10 +15077,10 @@
     </row>
     <row r="25" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="C25" s="7">
         <v>38</v>
@@ -14848,10 +15092,10 @@
         <v>3</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>39</v>
@@ -14859,10 +15103,10 @@
     </row>
     <row r="26" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="C26" s="7">
         <v>34</v>
@@ -14874,10 +15118,10 @@
         <v>3</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>39</v>
@@ -14885,10 +15129,10 @@
     </row>
     <row r="27" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
       <c r="C27" s="7">
         <v>60</v>
@@ -14900,10 +15144,10 @@
         <v>3</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>39</v>
@@ -14911,10 +15155,10 @@
     </row>
     <row r="28" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="C28" s="7">
         <v>8</v>
@@ -14926,10 +15170,10 @@
         <v>3</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>39</v>
@@ -14937,10 +15181,10 @@
     </row>
     <row r="29" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
       <c r="C29" s="7">
         <v>14</v>
@@ -14952,10 +15196,10 @@
         <v>3</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>39</v>
@@ -14963,10 +15207,10 @@
     </row>
     <row r="30" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="C30" s="7">
         <v>30</v>
@@ -14978,10 +15222,10 @@
         <v>3</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>39</v>
@@ -14989,10 +15233,10 @@
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="C31" s="7">
         <v>5</v>
@@ -15004,10 +15248,10 @@
         <v>3</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>39</v>

--- a/balance/LIFE-баланс.xlsx
+++ b/balance/LIFE-баланс.xlsx
@@ -30,12 +30,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3696" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3682" uniqueCount="835">
   <si>
     <t>ЖИЗНЬ — таблица баланса</t>
   </si>
   <si>
-    <t>Версия выгрузки: Альфа 0.16.0</t>
+    <t>Версия выгрузки: Альфа 0.17.0</t>
   </si>
   <si>
     <t>Дата: 2026-08-20</t>
@@ -2099,7 +2099,7 @@
     <t>цепочка</t>
   </si>
   <si>
-    <t>Столько циклов подряд с зайцами = устойчивая цепочка (открывает медведя и эру).</t>
+    <t>Столько циклов подряд с зайцами = устойчивая цепочка (открывает медведя и потолок ⚡).</t>
   </si>
   <si>
     <t>arcade.arcadeEnd.noAnimalRenewalGens</t>
@@ -2118,15 +2118,6 @@
   </si>
   <si>
     <t>Раз в столько циклов начисляются очки survival при живой пирамиде.</t>
-  </si>
-  <si>
-    <t>arcade.arcadeEnd.eraAfterChain</t>
-  </si>
-  <si>
-    <t>длина эры</t>
-  </si>
-  <si>
-    <t>После устойчивой цепочки ещё столько циклов — и раунд кончается победой. 0 = бесконечная ферма.</t>
   </si>
   <si>
     <t>arcade.roulette.interval</t>
@@ -3408,57 +3399,57 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>815</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>816</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>817</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>818</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>819</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>820</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>821</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>822</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>823</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>824</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>825</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>826</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>827</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>3</v>
@@ -3508,7 +3499,7 @@
     </row>
     <row r="3" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>57</v>
@@ -3558,7 +3549,7 @@
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>60</v>
@@ -3608,7 +3599,7 @@
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>63</v>
@@ -3658,7 +3649,7 @@
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>426</v>
@@ -3708,7 +3699,7 @@
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>430</v>
@@ -3758,7 +3749,7 @@
     </row>
     <row r="8" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>433</v>
@@ -3808,7 +3799,7 @@
     </row>
     <row r="9" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>436</v>
@@ -3858,7 +3849,7 @@
     </row>
     <row r="10" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>421</v>
@@ -6304,7 +6295,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -6525,34 +6516,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>697</v>
-      </c>
-      <c r="C9" s="8">
-        <v>300</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>698</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>677</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H9"/>
+  <autoFilter ref="A1:H8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -6604,10 +6569,10 @@
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C2" s="8">
         <v>100</v>
@@ -6619,10 +6584,10 @@
         <v>246</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>55</v>
@@ -6630,10 +6595,10 @@
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C3" s="8">
         <v>30</v>
@@ -6645,10 +6610,10 @@
         <v>3</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>55</v>
@@ -6656,10 +6621,10 @@
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C4" s="8">
         <v>30</v>
@@ -6671,10 +6636,10 @@
         <v>3</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>55</v>
@@ -6682,10 +6647,10 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C5" s="8">
         <v>25</v>
@@ -6697,10 +6662,10 @@
         <v>3</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>55</v>
@@ -6708,10 +6673,10 @@
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C6" s="8">
         <v>15</v>
@@ -6723,10 +6688,10 @@
         <v>3</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>55</v>
@@ -6734,10 +6699,10 @@
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="C7" s="8">
         <v>0.1</v>
@@ -6749,10 +6714,10 @@
         <v>3</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>55</v>
@@ -6760,10 +6725,10 @@
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C8" s="8">
         <v>0.3</v>
@@ -6775,10 +6740,10 @@
         <v>3</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>55</v>
@@ -6786,10 +6751,10 @@
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="C9" s="8">
         <v>0.1</v>
@@ -6801,10 +6766,10 @@
         <v>3</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>55</v>
@@ -6812,10 +6777,10 @@
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C10" s="8">
         <v>0.5</v>
@@ -6827,10 +6792,10 @@
         <v>3</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>55</v>
@@ -6838,10 +6803,10 @@
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C11" s="8">
         <v>0.1</v>
@@ -6853,10 +6818,10 @@
         <v>3</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>55</v>
@@ -6864,10 +6829,10 @@
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C12" s="8">
         <v>0.3</v>
@@ -6879,10 +6844,10 @@
         <v>3</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>55</v>
@@ -6890,10 +6855,10 @@
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C13" s="8">
         <v>0.5</v>
@@ -6905,10 +6870,10 @@
         <v>3</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>55</v>
@@ -6916,10 +6881,10 @@
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C14" s="8">
         <v>1</v>
@@ -6931,10 +6896,10 @@
         <v>3</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>55</v>
@@ -6942,10 +6907,10 @@
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="C15" s="8">
         <v>0.0015</v>
@@ -6957,10 +6922,10 @@
         <v>3</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>55</v>
@@ -6968,10 +6933,10 @@
     </row>
     <row r="16" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C16" s="8">
         <v>1.8</v>
@@ -6983,10 +6948,10 @@
         <v>3</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>55</v>
@@ -6994,10 +6959,10 @@
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="C17" s="8">
         <v>45</v>
@@ -7009,10 +6974,10 @@
         <v>3</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>55</v>
@@ -7020,10 +6985,10 @@
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C18" s="8">
         <v>28</v>
@@ -7035,10 +7000,10 @@
         <v>3</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>55</v>
@@ -7155,7 +7120,7 @@
         <v>45</v>
       </c>
       <c r="C4" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>42</v>
@@ -7211,7 +7176,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:H277"/>
+  <dimension ref="A1:H276"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -7310,7 +7275,7 @@
         <v>45</v>
       </c>
       <c r="C4" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>42</v>
@@ -13186,7 +13151,7 @@
         <v>697</v>
       </c>
       <c r="C230" s="8">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D230" s="5" t="s">
         <v>42</v>
@@ -13198,7 +13163,7 @@
         <v>698</v>
       </c>
       <c r="G230" s="5" t="s">
-        <v>677</v>
+        <v>699</v>
       </c>
       <c r="H230" s="5" t="s">
         <v>55</v>
@@ -13206,25 +13171,25 @@
     </row>
     <row r="231" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="C231" s="8">
+        <v>30</v>
+      </c>
+      <c r="D231" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E231" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F231" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="G231" s="5" t="s">
         <v>699</v>
-      </c>
-      <c r="B231" s="5" t="s">
-        <v>700</v>
-      </c>
-      <c r="C231" s="8">
-        <v>100</v>
-      </c>
-      <c r="D231" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E231" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="F231" s="5" t="s">
-        <v>701</v>
-      </c>
-      <c r="G231" s="5" t="s">
-        <v>702</v>
       </c>
       <c r="H231" s="5" t="s">
         <v>55</v>
@@ -13250,7 +13215,7 @@
         <v>705</v>
       </c>
       <c r="G232" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H232" s="5" t="s">
         <v>55</v>
@@ -13264,7 +13229,7 @@
         <v>707</v>
       </c>
       <c r="C233" s="8">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D233" s="5" t="s">
         <v>42</v>
@@ -13276,7 +13241,7 @@
         <v>708</v>
       </c>
       <c r="G233" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H233" s="5" t="s">
         <v>55</v>
@@ -13290,7 +13255,7 @@
         <v>710</v>
       </c>
       <c r="C234" s="8">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D234" s="5" t="s">
         <v>42</v>
@@ -13302,7 +13267,7 @@
         <v>711</v>
       </c>
       <c r="G234" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H234" s="5" t="s">
         <v>55</v>
@@ -13316,7 +13281,7 @@
         <v>713</v>
       </c>
       <c r="C235" s="8">
-        <v>15</v>
+        <v>0.1</v>
       </c>
       <c r="D235" s="5" t="s">
         <v>42</v>
@@ -13328,7 +13293,7 @@
         <v>714</v>
       </c>
       <c r="G235" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H235" s="5" t="s">
         <v>55</v>
@@ -13342,7 +13307,7 @@
         <v>716</v>
       </c>
       <c r="C236" s="8">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D236" s="5" t="s">
         <v>42</v>
@@ -13354,7 +13319,7 @@
         <v>717</v>
       </c>
       <c r="G236" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H236" s="5" t="s">
         <v>55</v>
@@ -13368,7 +13333,7 @@
         <v>719</v>
       </c>
       <c r="C237" s="8">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="D237" s="5" t="s">
         <v>42</v>
@@ -13380,7 +13345,7 @@
         <v>720</v>
       </c>
       <c r="G237" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H237" s="5" t="s">
         <v>55</v>
@@ -13394,7 +13359,7 @@
         <v>722</v>
       </c>
       <c r="C238" s="8">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D238" s="5" t="s">
         <v>42</v>
@@ -13406,7 +13371,7 @@
         <v>723</v>
       </c>
       <c r="G238" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H238" s="5" t="s">
         <v>55</v>
@@ -13420,7 +13385,7 @@
         <v>725</v>
       </c>
       <c r="C239" s="8">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="D239" s="5" t="s">
         <v>42</v>
@@ -13432,7 +13397,7 @@
         <v>726</v>
       </c>
       <c r="G239" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H239" s="5" t="s">
         <v>55</v>
@@ -13446,7 +13411,7 @@
         <v>728</v>
       </c>
       <c r="C240" s="8">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D240" s="5" t="s">
         <v>42</v>
@@ -13458,7 +13423,7 @@
         <v>729</v>
       </c>
       <c r="G240" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H240" s="5" t="s">
         <v>55</v>
@@ -13472,7 +13437,7 @@
         <v>731</v>
       </c>
       <c r="C241" s="8">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D241" s="5" t="s">
         <v>42</v>
@@ -13484,7 +13449,7 @@
         <v>732</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H241" s="5" t="s">
         <v>55</v>
@@ -13498,7 +13463,7 @@
         <v>734</v>
       </c>
       <c r="C242" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D242" s="5" t="s">
         <v>42</v>
@@ -13510,7 +13475,7 @@
         <v>735</v>
       </c>
       <c r="G242" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H242" s="5" t="s">
         <v>55</v>
@@ -13524,7 +13489,7 @@
         <v>737</v>
       </c>
       <c r="C243" s="8">
-        <v>1</v>
+        <v>0.0015</v>
       </c>
       <c r="D243" s="5" t="s">
         <v>42</v>
@@ -13536,7 +13501,7 @@
         <v>738</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H243" s="5" t="s">
         <v>55</v>
@@ -13550,7 +13515,7 @@
         <v>740</v>
       </c>
       <c r="C244" s="8">
-        <v>0.0015</v>
+        <v>1.8</v>
       </c>
       <c r="D244" s="5" t="s">
         <v>42</v>
@@ -13562,7 +13527,7 @@
         <v>741</v>
       </c>
       <c r="G244" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H244" s="5" t="s">
         <v>55</v>
@@ -13576,7 +13541,7 @@
         <v>743</v>
       </c>
       <c r="C245" s="8">
-        <v>1.8</v>
+        <v>45</v>
       </c>
       <c r="D245" s="5" t="s">
         <v>42</v>
@@ -13588,7 +13553,7 @@
         <v>744</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H245" s="5" t="s">
         <v>55</v>
@@ -13602,7 +13567,7 @@
         <v>746</v>
       </c>
       <c r="C246" s="8">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D246" s="5" t="s">
         <v>42</v>
@@ -13614,7 +13579,7 @@
         <v>747</v>
       </c>
       <c r="G246" s="5" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H246" s="5" t="s">
         <v>55</v>
@@ -13627,8 +13592,8 @@
       <c r="B247" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="C247" s="8">
-        <v>28</v>
+      <c r="C247" s="7">
+        <v>2</v>
       </c>
       <c r="D247" s="5" t="s">
         <v>42</v>
@@ -13640,33 +13605,33 @@
         <v>750</v>
       </c>
       <c r="G247" s="5" t="s">
-        <v>702</v>
+        <v>751</v>
       </c>
       <c r="H247" s="5" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
     </row>
     <row r="248" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="C248" s="7">
+        <v>4</v>
+      </c>
+      <c r="D248" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E248" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F248" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="G248" s="5" t="s">
         <v>751</v>
-      </c>
-      <c r="B248" s="5" t="s">
-        <v>752</v>
-      </c>
-      <c r="C248" s="7">
-        <v>2</v>
-      </c>
-      <c r="D248" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E248" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F248" s="5" t="s">
-        <v>753</v>
-      </c>
-      <c r="G248" s="5" t="s">
-        <v>754</v>
       </c>
       <c r="H248" s="5" t="s">
         <v>39</v>
@@ -13680,7 +13645,7 @@
         <v>756</v>
       </c>
       <c r="C249" s="7">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D249" s="5" t="s">
         <v>42</v>
@@ -13689,10 +13654,10 @@
         <v>3</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G249" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H249" s="5" t="s">
         <v>39</v>
@@ -13700,13 +13665,13 @@
     </row>
     <row r="250" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="B250" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="B250" s="5" t="s">
-        <v>759</v>
-      </c>
       <c r="C250" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D250" s="5" t="s">
         <v>42</v>
@@ -13715,10 +13680,10 @@
         <v>3</v>
       </c>
       <c r="F250" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G250" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H250" s="5" t="s">
         <v>39</v>
@@ -13726,13 +13691,13 @@
     </row>
     <row r="251" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="B251" s="5" t="s">
         <v>760</v>
       </c>
-      <c r="B251" s="5" t="s">
-        <v>761</v>
-      </c>
       <c r="C251" s="7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D251" s="5" t="s">
         <v>42</v>
@@ -13741,10 +13706,10 @@
         <v>3</v>
       </c>
       <c r="F251" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G251" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H251" s="5" t="s">
         <v>39</v>
@@ -13752,13 +13717,13 @@
     </row>
     <row r="252" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="B252" s="5" t="s">
         <v>762</v>
       </c>
-      <c r="B252" s="5" t="s">
-        <v>763</v>
-      </c>
       <c r="C252" s="7">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D252" s="5" t="s">
         <v>42</v>
@@ -13767,10 +13732,10 @@
         <v>3</v>
       </c>
       <c r="F252" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G252" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H252" s="5" t="s">
         <v>39</v>
@@ -13778,13 +13743,13 @@
     </row>
     <row r="253" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="B253" s="5" t="s">
         <v>764</v>
       </c>
-      <c r="B253" s="5" t="s">
-        <v>765</v>
-      </c>
       <c r="C253" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D253" s="5" t="s">
         <v>42</v>
@@ -13793,10 +13758,10 @@
         <v>3</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G253" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H253" s="5" t="s">
         <v>39</v>
@@ -13804,13 +13769,13 @@
     </row>
     <row r="254" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B254" s="5" t="s">
         <v>766</v>
       </c>
-      <c r="B254" s="5" t="s">
-        <v>767</v>
-      </c>
       <c r="C254" s="7">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D254" s="5" t="s">
         <v>42</v>
@@ -13819,10 +13784,10 @@
         <v>3</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G254" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H254" s="5" t="s">
         <v>39</v>
@@ -13830,13 +13795,13 @@
     </row>
     <row r="255" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="B255" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="B255" s="5" t="s">
-        <v>769</v>
-      </c>
       <c r="C255" s="7">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D255" s="5" t="s">
         <v>42</v>
@@ -13845,10 +13810,10 @@
         <v>3</v>
       </c>
       <c r="F255" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G255" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H255" s="5" t="s">
         <v>39</v>
@@ -13856,13 +13821,13 @@
     </row>
     <row r="256" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="B256" s="5" t="s">
         <v>770</v>
       </c>
-      <c r="B256" s="5" t="s">
-        <v>771</v>
-      </c>
       <c r="C256" s="7">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D256" s="5" t="s">
         <v>42</v>
@@ -13871,10 +13836,10 @@
         <v>3</v>
       </c>
       <c r="F256" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G256" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H256" s="5" t="s">
         <v>39</v>
@@ -13882,13 +13847,13 @@
     </row>
     <row r="257" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="B257" s="5" t="s">
         <v>772</v>
       </c>
-      <c r="B257" s="5" t="s">
-        <v>773</v>
-      </c>
       <c r="C257" s="7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D257" s="5" t="s">
         <v>42</v>
@@ -13897,10 +13862,10 @@
         <v>3</v>
       </c>
       <c r="F257" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G257" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H257" s="5" t="s">
         <v>39</v>
@@ -13908,13 +13873,13 @@
     </row>
     <row r="258" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="B258" s="5" t="s">
         <v>774</v>
       </c>
-      <c r="B258" s="5" t="s">
-        <v>775</v>
-      </c>
       <c r="C258" s="7">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D258" s="5" t="s">
         <v>42</v>
@@ -13923,10 +13888,10 @@
         <v>3</v>
       </c>
       <c r="F258" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G258" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H258" s="5" t="s">
         <v>39</v>
@@ -13934,13 +13899,13 @@
     </row>
     <row r="259" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="B259" s="5" t="s">
         <v>776</v>
       </c>
-      <c r="B259" s="5" t="s">
-        <v>777</v>
-      </c>
       <c r="C259" s="7">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D259" s="5" t="s">
         <v>42</v>
@@ -13949,10 +13914,10 @@
         <v>3</v>
       </c>
       <c r="F259" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G259" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H259" s="5" t="s">
         <v>39</v>
@@ -13960,13 +13925,13 @@
     </row>
     <row r="260" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="B260" s="5" t="s">
         <v>778</v>
       </c>
-      <c r="B260" s="5" t="s">
-        <v>779</v>
-      </c>
       <c r="C260" s="7">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="D260" s="5" t="s">
         <v>42</v>
@@ -13975,10 +13940,10 @@
         <v>3</v>
       </c>
       <c r="F260" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G260" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H260" s="5" t="s">
         <v>39</v>
@@ -13986,13 +13951,13 @@
     </row>
     <row r="261" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="B261" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="B261" s="5" t="s">
-        <v>781</v>
-      </c>
       <c r="C261" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D261" s="5" t="s">
         <v>42</v>
@@ -14001,10 +13966,10 @@
         <v>3</v>
       </c>
       <c r="F261" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G261" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H261" s="5" t="s">
         <v>39</v>
@@ -14012,13 +13977,13 @@
     </row>
     <row r="262" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="5" t="s">
+        <v>781</v>
+      </c>
+      <c r="B262" s="5" t="s">
         <v>782</v>
       </c>
-      <c r="B262" s="5" t="s">
-        <v>783</v>
-      </c>
       <c r="C262" s="7">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D262" s="5" t="s">
         <v>42</v>
@@ -14027,10 +13992,10 @@
         <v>3</v>
       </c>
       <c r="F262" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G262" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H262" s="5" t="s">
         <v>39</v>
@@ -14038,13 +14003,13 @@
     </row>
     <row r="263" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="5" t="s">
+        <v>783</v>
+      </c>
+      <c r="B263" s="5" t="s">
         <v>784</v>
       </c>
-      <c r="B263" s="5" t="s">
-        <v>785</v>
-      </c>
       <c r="C263" s="7">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D263" s="5" t="s">
         <v>42</v>
@@ -14053,10 +14018,10 @@
         <v>3</v>
       </c>
       <c r="F263" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G263" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H263" s="5" t="s">
         <v>39</v>
@@ -14064,13 +14029,13 @@
     </row>
     <row r="264" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="B264" s="5" t="s">
         <v>786</v>
       </c>
-      <c r="B264" s="5" t="s">
-        <v>787</v>
-      </c>
       <c r="C264" s="7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D264" s="5" t="s">
         <v>42</v>
@@ -14079,10 +14044,10 @@
         <v>3</v>
       </c>
       <c r="F264" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G264" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H264" s="5" t="s">
         <v>39</v>
@@ -14090,13 +14055,13 @@
     </row>
     <row r="265" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="B265" s="5" t="s">
         <v>788</v>
       </c>
-      <c r="B265" s="5" t="s">
-        <v>789</v>
-      </c>
       <c r="C265" s="7">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D265" s="5" t="s">
         <v>42</v>
@@ -14105,10 +14070,10 @@
         <v>3</v>
       </c>
       <c r="F265" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G265" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H265" s="5" t="s">
         <v>39</v>
@@ -14116,13 +14081,13 @@
     </row>
     <row r="266" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="B266" s="5" t="s">
         <v>790</v>
       </c>
-      <c r="B266" s="5" t="s">
-        <v>791</v>
-      </c>
       <c r="C266" s="7">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D266" s="5" t="s">
         <v>42</v>
@@ -14131,10 +14096,10 @@
         <v>3</v>
       </c>
       <c r="F266" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G266" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H266" s="5" t="s">
         <v>39</v>
@@ -14142,10 +14107,10 @@
     </row>
     <row r="267" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="B267" s="5" t="s">
         <v>792</v>
-      </c>
-      <c r="B267" s="5" t="s">
-        <v>793</v>
       </c>
       <c r="C267" s="7">
         <v>35</v>
@@ -14157,10 +14122,10 @@
         <v>3</v>
       </c>
       <c r="F267" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G267" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H267" s="5" t="s">
         <v>39</v>
@@ -14168,13 +14133,13 @@
     </row>
     <row r="268" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="B268" s="5" t="s">
         <v>794</v>
       </c>
-      <c r="B268" s="5" t="s">
-        <v>795</v>
-      </c>
       <c r="C268" s="7">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D268" s="5" t="s">
         <v>42</v>
@@ -14183,10 +14148,10 @@
         <v>3</v>
       </c>
       <c r="F268" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G268" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H268" s="5" t="s">
         <v>39</v>
@@ -14194,13 +14159,13 @@
     </row>
     <row r="269" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B269" s="5" t="s">
         <v>796</v>
       </c>
-      <c r="B269" s="5" t="s">
-        <v>797</v>
-      </c>
       <c r="C269" s="7">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D269" s="5" t="s">
         <v>42</v>
@@ -14209,10 +14174,10 @@
         <v>3</v>
       </c>
       <c r="F269" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G269" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H269" s="5" t="s">
         <v>39</v>
@@ -14220,13 +14185,13 @@
     </row>
     <row r="270" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="B270" s="5" t="s">
         <v>798</v>
       </c>
-      <c r="B270" s="5" t="s">
-        <v>799</v>
-      </c>
       <c r="C270" s="7">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D270" s="5" t="s">
         <v>42</v>
@@ -14235,10 +14200,10 @@
         <v>3</v>
       </c>
       <c r="F270" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G270" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H270" s="5" t="s">
         <v>39</v>
@@ -14246,13 +14211,13 @@
     </row>
     <row r="271" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="B271" s="5" t="s">
         <v>800</v>
       </c>
-      <c r="B271" s="5" t="s">
-        <v>801</v>
-      </c>
       <c r="C271" s="7">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D271" s="5" t="s">
         <v>42</v>
@@ -14261,10 +14226,10 @@
         <v>3</v>
       </c>
       <c r="F271" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G271" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H271" s="5" t="s">
         <v>39</v>
@@ -14272,13 +14237,13 @@
     </row>
     <row r="272" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="B272" s="5" t="s">
         <v>802</v>
       </c>
-      <c r="B272" s="5" t="s">
-        <v>803</v>
-      </c>
       <c r="C272" s="7">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D272" s="5" t="s">
         <v>42</v>
@@ -14287,10 +14252,10 @@
         <v>3</v>
       </c>
       <c r="F272" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G272" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H272" s="5" t="s">
         <v>39</v>
@@ -14298,13 +14263,13 @@
     </row>
     <row r="273" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="B273" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="B273" s="5" t="s">
-        <v>805</v>
-      </c>
       <c r="C273" s="7">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D273" s="5" t="s">
         <v>42</v>
@@ -14313,10 +14278,10 @@
         <v>3</v>
       </c>
       <c r="F273" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G273" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H273" s="5" t="s">
         <v>39</v>
@@ -14324,13 +14289,13 @@
     </row>
     <row r="274" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="B274" s="5" t="s">
         <v>806</v>
       </c>
-      <c r="B274" s="5" t="s">
-        <v>807</v>
-      </c>
       <c r="C274" s="7">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D274" s="5" t="s">
         <v>42</v>
@@ -14339,10 +14304,10 @@
         <v>3</v>
       </c>
       <c r="F274" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G274" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H274" s="5" t="s">
         <v>39</v>
@@ -14350,13 +14315,13 @@
     </row>
     <row r="275" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="B275" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="B275" s="5" t="s">
-        <v>809</v>
-      </c>
       <c r="C275" s="7">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D275" s="5" t="s">
         <v>42</v>
@@ -14365,10 +14330,10 @@
         <v>3</v>
       </c>
       <c r="F275" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G275" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H275" s="5" t="s">
         <v>39</v>
@@ -14376,13 +14341,13 @@
     </row>
     <row r="276" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="B276" s="5" t="s">
         <v>810</v>
       </c>
-      <c r="B276" s="5" t="s">
-        <v>811</v>
-      </c>
       <c r="C276" s="7">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D276" s="5" t="s">
         <v>42</v>
@@ -14391,43 +14356,17 @@
         <v>3</v>
       </c>
       <c r="F276" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G276" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H276" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="277" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A277" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="B277" s="5" t="s">
-        <v>813</v>
-      </c>
-      <c r="C277" s="7">
-        <v>5</v>
-      </c>
-      <c r="D277" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E277" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F277" s="5" t="s">
-        <v>757</v>
-      </c>
-      <c r="G277" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="H277" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H277"/>
+  <autoFilter ref="A1:H276"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -14479,10 +14418,10 @@
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="C2" s="7">
         <v>2</v>
@@ -14494,10 +14433,10 @@
         <v>3</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>39</v>
@@ -14505,10 +14444,10 @@
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="C3" s="7">
         <v>4</v>
@@ -14520,10 +14459,10 @@
         <v>3</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>39</v>
@@ -14531,10 +14470,10 @@
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="C4" s="7">
         <v>12</v>
@@ -14546,10 +14485,10 @@
         <v>3</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>39</v>
@@ -14557,10 +14496,10 @@
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="C5" s="7">
         <v>8</v>
@@ -14572,10 +14511,10 @@
         <v>3</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>39</v>
@@ -14583,10 +14522,10 @@
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C6" s="7">
         <v>3</v>
@@ -14598,10 +14537,10 @@
         <v>3</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>39</v>
@@ -14609,10 +14548,10 @@
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C7" s="7">
         <v>8</v>
@@ -14624,10 +14563,10 @@
         <v>3</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>39</v>
@@ -14635,10 +14574,10 @@
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="C8" s="7">
         <v>12</v>
@@ -14650,10 +14589,10 @@
         <v>3</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>39</v>
@@ -14661,10 +14600,10 @@
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="C9" s="7">
         <v>24</v>
@@ -14676,10 +14615,10 @@
         <v>3</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>39</v>
@@ -14687,10 +14626,10 @@
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C10" s="7">
         <v>14</v>
@@ -14702,10 +14641,10 @@
         <v>3</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>39</v>
@@ -14713,10 +14652,10 @@
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C11" s="7">
         <v>20</v>
@@ -14728,10 +14667,10 @@
         <v>3</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>39</v>
@@ -14739,10 +14678,10 @@
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="C12" s="7">
         <v>22</v>
@@ -14754,10 +14693,10 @@
         <v>3</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>39</v>
@@ -14765,10 +14704,10 @@
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="C13" s="7">
         <v>30</v>
@@ -14780,10 +14719,10 @@
         <v>3</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>39</v>
@@ -14791,10 +14730,10 @@
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C14" s="7">
         <v>40</v>
@@ -14806,10 +14745,10 @@
         <v>3</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>39</v>
@@ -14817,10 +14756,10 @@
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="C15" s="7">
         <v>5</v>
@@ -14832,10 +14771,10 @@
         <v>3</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>39</v>
@@ -14843,10 +14782,10 @@
     </row>
     <row r="16" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C16" s="7">
         <v>8</v>
@@ -14858,10 +14797,10 @@
         <v>3</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>39</v>
@@ -14869,10 +14808,10 @@
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C17" s="7">
         <v>18</v>
@@ -14884,10 +14823,10 @@
         <v>3</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>39</v>
@@ -14895,10 +14834,10 @@
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C18" s="7">
         <v>10</v>
@@ -14910,10 +14849,10 @@
         <v>3</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>39</v>
@@ -14921,10 +14860,10 @@
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C19" s="7">
         <v>16</v>
@@ -14936,10 +14875,10 @@
         <v>3</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>39</v>
@@ -14947,10 +14886,10 @@
     </row>
     <row r="20" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="C20" s="7">
         <v>20</v>
@@ -14962,10 +14901,10 @@
         <v>3</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>39</v>
@@ -14973,10 +14912,10 @@
     </row>
     <row r="21" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C21" s="7">
         <v>35</v>
@@ -14988,10 +14927,10 @@
         <v>3</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>39</v>
@@ -14999,10 +14938,10 @@
     </row>
     <row r="22" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C22" s="7">
         <v>35</v>
@@ -15014,10 +14953,10 @@
         <v>3</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>39</v>
@@ -15025,10 +14964,10 @@
     </row>
     <row r="23" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C23" s="7">
         <v>25</v>
@@ -15040,10 +14979,10 @@
         <v>3</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>39</v>
@@ -15051,10 +14990,10 @@
     </row>
     <row r="24" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C24" s="7">
         <v>32</v>
@@ -15066,10 +15005,10 @@
         <v>3</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>39</v>
@@ -15077,10 +15016,10 @@
     </row>
     <row r="25" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="C25" s="7">
         <v>38</v>
@@ -15092,10 +15031,10 @@
         <v>3</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>39</v>
@@ -15103,10 +15042,10 @@
     </row>
     <row r="26" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="C26" s="7">
         <v>34</v>
@@ -15118,10 +15057,10 @@
         <v>3</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>39</v>
@@ -15129,10 +15068,10 @@
     </row>
     <row r="27" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="C27" s="7">
         <v>60</v>
@@ -15144,10 +15083,10 @@
         <v>3</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>39</v>
@@ -15155,10 +15094,10 @@
     </row>
     <row r="28" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="C28" s="7">
         <v>8</v>
@@ -15170,10 +15109,10 @@
         <v>3</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>39</v>
@@ -15181,10 +15120,10 @@
     </row>
     <row r="29" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="C29" s="7">
         <v>14</v>
@@ -15196,10 +15135,10 @@
         <v>3</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>39</v>
@@ -15207,10 +15146,10 @@
     </row>
     <row r="30" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C30" s="7">
         <v>30</v>
@@ -15222,10 +15161,10 @@
         <v>3</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>39</v>
@@ -15233,10 +15172,10 @@
     </row>
     <row r="31" ht="32" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C31" s="7">
         <v>5</v>
@@ -15248,10 +15187,10 @@
         <v>3</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>39</v>
